--- a/Packages/cn.etetet.twsmmo/Luban/Config/Datas/Action.xlsx
+++ b/Packages/cn.etetet.twsmmo/Luban/Config/Datas/Action.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
   <si>
     <t>##var</t>
   </si>
@@ -47,7 +47,7 @@
     <t>int</t>
   </si>
   <si>
-    <t>(list#sep=,),string</t>
+    <t>(list#sep=,),int</t>
   </si>
   <si>
     <t>##</t>
@@ -57,6 +57,15 @@
   </si>
   <si>
     <t>参数</t>
+  </si>
+  <si>
+    <t>伤害</t>
+  </si>
+  <si>
+    <t>子弹</t>
+  </si>
+  <si>
+    <t>1000,12</t>
   </si>
 </sst>
 </file>
@@ -691,8 +700,12 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1015,12 +1028,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="22.5" outlineLevelRow="3" outlineLevelCol="3"/>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="22.5" outlineLevelRow="4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="12.5" style="2" customWidth="1"/>
     <col min="2" max="2" width="15.875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="15.75" style="2" customWidth="1"/>
+    <col min="3" max="3" width="18.5" style="2" customWidth="1"/>
     <col min="4" max="5" width="26.875" style="2" customWidth="1"/>
     <col min="6" max="6" width="23.75" style="2" customWidth="1"/>
     <col min="7" max="7" width="29.375" style="2" customWidth="1"/>
@@ -1049,7 +1062,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>6</v>
@@ -1069,9 +1082,26 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" spans="2:2">
+    <row r="4" s="2" customFormat="1" spans="2:4">
       <c r="B4" s="3">
-        <v>1</v>
+        <v>1001</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="2">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4">
+      <c r="B5" s="2">
+        <v>1002</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/Packages/cn.etetet.twsmmo/Luban/Config/Datas/Action.xlsx
+++ b/Packages/cn.etetet.twsmmo/Luban/Config/Datas/Action.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="21600"/>
   </bookViews>
   <sheets>
     <sheet name="ActionsConfig" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="55">
   <si>
     <t>##var</t>
   </si>
@@ -35,10 +35,13 @@
     <t>Id</t>
   </si>
   <si>
+    <t>#Desc</t>
+  </si>
+  <si>
     <t>ActionType</t>
   </si>
   <si>
-    <t>Param</t>
+    <t>NumericType</t>
   </si>
   <si>
     <t>##type</t>
@@ -47,25 +50,148 @@
     <t>int</t>
   </si>
   <si>
-    <t>(list#sep=,),int</t>
+    <t>string</t>
+  </si>
+  <si>
+    <t>ENumericType</t>
   </si>
   <si>
     <t>##</t>
   </si>
   <si>
+    <t>行为描述</t>
+  </si>
+  <si>
     <t>技能行为类型</t>
   </si>
   <si>
-    <t>参数</t>
+    <t>数值类型</t>
+  </si>
+  <si>
+    <t>造成伤害</t>
   </si>
   <si>
     <t>伤害</t>
   </si>
   <si>
-    <t>子弹</t>
-  </si>
-  <si>
-    <t>1000,12</t>
+    <t>当前血量_0</t>
+  </si>
+  <si>
+    <t>增加移动速度</t>
+  </si>
+  <si>
+    <t>数值</t>
+  </si>
+  <si>
+    <t>速度_1</t>
+  </si>
+  <si>
+    <t>增加范围</t>
+  </si>
+  <si>
+    <t>攻击范围_1</t>
+  </si>
+  <si>
+    <t>增加血量上限</t>
+  </si>
+  <si>
+    <t>最大血量_1</t>
+  </si>
+  <si>
+    <t>增加经验获取</t>
+  </si>
+  <si>
+    <t>对局经验值倍率_0</t>
+  </si>
+  <si>
+    <t>降低受到的伤害</t>
+  </si>
+  <si>
+    <t>防御_1</t>
+  </si>
+  <si>
+    <t>减少攻击间隔</t>
+  </si>
+  <si>
+    <t>攻击间隔_1</t>
+  </si>
+  <si>
+    <t>增加道具吸收范围</t>
+  </si>
+  <si>
+    <t>吸收范围_1</t>
+  </si>
+  <si>
+    <t>增加攻击</t>
+  </si>
+  <si>
+    <t>普攻伤害_1</t>
+  </si>
+  <si>
+    <t>增加金币获取</t>
+  </si>
+  <si>
+    <t>对局金币倍率_0</t>
+  </si>
+  <si>
+    <t>延长持续效果</t>
+  </si>
+  <si>
+    <t>技能触发间隔_1</t>
+  </si>
+  <si>
+    <t>恢复血量</t>
+  </si>
+  <si>
+    <t>创建技能</t>
+  </si>
+  <si>
+    <t>无</t>
+  </si>
+  <si>
+    <t>物体移动方向为当前物体移动方向（需设定移动速度）</t>
+  </si>
+  <si>
+    <t>移动方向直线移动</t>
+  </si>
+  <si>
+    <t>当前物体正前方向直线移动（需设定移动速度）</t>
+  </si>
+  <si>
+    <t>正前方直线移动</t>
+  </si>
+  <si>
+    <t>曲线运动</t>
+  </si>
+  <si>
+    <t>曲线移动</t>
+  </si>
+  <si>
+    <t>随机位置</t>
+  </si>
+  <si>
+    <t>随机方向直线移动（需设定移动速度）</t>
+  </si>
+  <si>
+    <t>随机方向直线移动</t>
+  </si>
+  <si>
+    <t>创建特效</t>
+  </si>
+  <si>
+    <t>创建Buff</t>
+  </si>
+  <si>
+    <t>禁止移动</t>
+  </si>
+  <si>
+    <t>禁止移动_0</t>
+  </si>
+  <si>
+    <t>禁止跟随</t>
+  </si>
+  <si>
+    <t>禁止跟随_0</t>
   </si>
 </sst>
 </file>
@@ -698,12 +824,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1028,19 +1160,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="22.5" outlineLevelRow="4" outlineLevelCol="3"/>
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="22.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="12.5" style="2" customWidth="1"/>
     <col min="2" max="2" width="15.875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="18.5" style="2" customWidth="1"/>
-    <col min="4" max="5" width="26.875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="23.75" style="2" customWidth="1"/>
-    <col min="7" max="7" width="29.375" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="2"/>
+    <col min="3" max="3" width="70.75" style="2" customWidth="1"/>
+    <col min="4" max="4" width="24" style="2" customWidth="1"/>
+    <col min="5" max="5" width="22.375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="46.5" style="3" customWidth="1"/>
+    <col min="7" max="7" width="26.875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="23.75" style="2" customWidth="1"/>
+    <col min="9" max="9" width="29.375" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:4">
+    <row r="1" s="1" customFormat="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1053,55 +1188,375 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:4">
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4"/>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:4">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" s="2" customFormat="1" spans="2:4">
-      <c r="B4" s="3">
+        <v>11</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" s="2" customFormat="1" spans="2:6">
+      <c r="B4" s="5">
+        <f>IF(ISBLANK(C4),"",ROW()-3+1000)</f>
         <v>1001</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="2">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4">
-      <c r="B5" s="2">
+      <c r="C4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="3"/>
+    </row>
+    <row r="5" spans="2:5">
+      <c r="B5" s="5">
+        <f t="shared" ref="B5:B25" si="0">IF(ISBLANK(C5),"",ROW()-3+1000)</f>
         <v>1002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5">
+      <c r="B6" s="5">
+        <f t="shared" si="0"/>
+        <v>1003</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5">
+      <c r="B7" s="5">
+        <f t="shared" si="0"/>
+        <v>1004</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5">
+      <c r="B8" s="5">
+        <f t="shared" si="0"/>
+        <v>1005</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5">
+      <c r="B9" s="5">
+        <f t="shared" si="0"/>
+        <v>1006</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5">
+      <c r="B10" s="5">
+        <f t="shared" si="0"/>
+        <v>1007</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5">
+      <c r="B11" s="5">
+        <f t="shared" si="0"/>
+        <v>1008</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5">
+      <c r="B12" s="5">
+        <f t="shared" si="0"/>
+        <v>1009</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5">
+      <c r="B13" s="5">
+        <f t="shared" si="0"/>
+        <v>1010</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5">
+      <c r="B14" s="5">
+        <f t="shared" si="0"/>
+        <v>1011</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5">
+      <c r="B15" s="5">
+        <f t="shared" si="0"/>
+        <v>1012</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5">
+      <c r="B16" s="5">
+        <f t="shared" si="0"/>
+        <v>1013</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5">
+      <c r="B17" s="5">
+        <f t="shared" si="0"/>
+        <v>1014</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5">
+      <c r="B18" s="5">
+        <f t="shared" si="0"/>
+        <v>1015</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5">
+      <c r="B19" s="5">
+        <f t="shared" si="0"/>
+        <v>1016</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5">
+      <c r="B20" s="5">
+        <f t="shared" si="0"/>
+        <v>1017</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5">
+      <c r="B21" s="5">
+        <f t="shared" si="0"/>
+        <v>1018</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5">
+      <c r="B22" s="5">
+        <f t="shared" si="0"/>
+        <v>1019</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5">
+      <c r="B23" s="5">
+        <f t="shared" si="0"/>
+        <v>1020</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5">
+      <c r="B24" s="5">
+        <f t="shared" si="0"/>
+        <v>1021</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5">
+      <c r="B25" s="2">
+        <v>1023</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/Packages/cn.etetet.twsmmo/Luban/Config/Datas/Action.xlsx
+++ b/Packages/cn.etetet.twsmmo/Luban/Config/Datas/Action.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="60">
   <si>
     <t>##var</t>
   </si>
@@ -192,6 +192,21 @@
   </si>
   <si>
     <t>禁止跟随_0</t>
+  </si>
+  <si>
+    <t>碰撞销毁自身</t>
+  </si>
+  <si>
+    <t>向上抛物线</t>
+  </si>
+  <si>
+    <t>自动销毁</t>
+  </si>
+  <si>
+    <t>技能持续时间_1</t>
+  </si>
+  <si>
+    <t>碰撞转向</t>
   </si>
 </sst>
 </file>
@@ -1160,7 +1175,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="22.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="12.5" style="2" customWidth="1"/>
@@ -1247,7 +1262,7 @@
     </row>
     <row r="5" spans="2:5">
       <c r="B5" s="5">
-        <f t="shared" ref="B5:B25" si="0">IF(ISBLANK(C5),"",ROW()-3+1000)</f>
+        <f t="shared" ref="B5:B26" si="0">IF(ISBLANK(C5),"",ROW()-3+1000)</f>
         <v>1002</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -1546,8 +1561,9 @@
       </c>
     </row>
     <row r="25" spans="2:5">
-      <c r="B25" s="2">
-        <v>1023</v>
+      <c r="B25" s="5">
+        <f t="shared" si="0"/>
+        <v>1022</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>53</v>
@@ -1557,6 +1573,102 @@
       </c>
       <c r="E25" s="2" t="s">
         <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5">
+      <c r="B26" s="5">
+        <f t="shared" si="0"/>
+        <v>1023</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5">
+      <c r="B27" s="5">
+        <f t="shared" ref="B27:B35" si="1">IF(ISBLANK(C27),"",ROW()-3+1000)</f>
+        <v>1024</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5">
+      <c r="B28" s="5">
+        <f>IF(ISBLANK(C28),"",ROW()-3+1000)</f>
+        <v>1025</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5">
+      <c r="B29" s="5">
+        <f>IF(ISBLANK(C29),"",ROW()-3+1000)</f>
+        <v>1026</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2">
+      <c r="B30" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="2:2">
+      <c r="B31" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="2:2">
+      <c r="B32" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/Packages/cn.etetet.twsmmo/Luban/Config/Datas/Action.xlsx
+++ b/Packages/cn.etetet.twsmmo/Luban/Config/Datas/Action.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21600"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="ActionsConfig" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="64">
   <si>
     <t>##var</t>
   </si>
@@ -207,6 +207,18 @@
   </si>
   <si>
     <t>碰撞转向</t>
+  </si>
+  <si>
+    <t>回旋移动</t>
+  </si>
+  <si>
+    <t>设置位置</t>
+  </si>
+  <si>
+    <t>根据父级设置位置</t>
+  </si>
+  <si>
+    <t>向鼠标位置移动</t>
   </si>
 </sst>
 </file>
@@ -1592,7 +1604,7 @@
     </row>
     <row r="27" spans="2:5">
       <c r="B27" s="5">
-        <f t="shared" ref="B27:B35" si="1">IF(ISBLANK(C27),"",ROW()-3+1000)</f>
+        <f>IF(ISBLANK(C27),"",ROW()-3+1000)</f>
         <v>1024</v>
       </c>
       <c r="C27" s="2" t="s">
@@ -1635,39 +1647,75 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="2:2">
-      <c r="B30" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="31" spans="2:2">
-      <c r="B31" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="32" spans="2:2">
-      <c r="B32" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="33" spans="2:2">
-      <c r="B33" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+    <row r="30" spans="2:5">
+      <c r="B30" s="5">
+        <f>IF(ISBLANK(C30),"",ROW()-3+1000)</f>
+        <v>1027</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5">
+      <c r="B31" s="5">
+        <f>IF(ISBLANK(C31),"",ROW()-3+1000)</f>
+        <v>1028</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5">
+      <c r="B32" s="5">
+        <f>IF(ISBLANK(C32),"",ROW()-3+1000)</f>
+        <v>1029</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5">
+      <c r="B33" s="5">
+        <f>IF(ISBLANK(C33),"",ROW()-3+1000)</f>
+        <v>1030</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(C34),"",ROW()-3+1000)</f>
         <v/>
       </c>
     </row>
     <row r="35" spans="2:2">
       <c r="B35" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(C35),"",ROW()-3+1000)</f>
         <v/>
       </c>
     </row>

--- a/Packages/cn.etetet.twsmmo/Luban/Config/Datas/Action.xlsx
+++ b/Packages/cn.etetet.twsmmo/Luban/Config/Datas/Action.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="65">
   <si>
     <t>##var</t>
   </si>
@@ -219,6 +219,9 @@
   </si>
   <si>
     <t>向鼠标位置移动</t>
+  </si>
+  <si>
+    <t>向玩家移动</t>
   </si>
 </sst>
 </file>
@@ -1187,7 +1190,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="22.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="12.5" style="2" customWidth="1"/>
@@ -1274,7 +1277,7 @@
     </row>
     <row r="5" spans="2:5">
       <c r="B5" s="5">
-        <f t="shared" ref="B5:B26" si="0">IF(ISBLANK(C5),"",ROW()-3+1000)</f>
+        <f t="shared" ref="B5:B35" si="0">IF(ISBLANK(C5),"",ROW()-3+1000)</f>
         <v>1002</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -1604,7 +1607,7 @@
     </row>
     <row r="27" spans="2:5">
       <c r="B27" s="5">
-        <f>IF(ISBLANK(C27),"",ROW()-3+1000)</f>
+        <f t="shared" si="0"/>
         <v>1024</v>
       </c>
       <c r="C27" s="2" t="s">
@@ -1619,7 +1622,7 @@
     </row>
     <row r="28" spans="2:5">
       <c r="B28" s="5">
-        <f>IF(ISBLANK(C28),"",ROW()-3+1000)</f>
+        <f t="shared" si="0"/>
         <v>1025</v>
       </c>
       <c r="C28" s="2" t="s">
@@ -1634,7 +1637,7 @@
     </row>
     <row r="29" spans="2:5">
       <c r="B29" s="5">
-        <f>IF(ISBLANK(C29),"",ROW()-3+1000)</f>
+        <f t="shared" si="0"/>
         <v>1026</v>
       </c>
       <c r="C29" s="2" t="s">
@@ -1649,7 +1652,7 @@
     </row>
     <row r="30" spans="2:5">
       <c r="B30" s="5">
-        <f>IF(ISBLANK(C30),"",ROW()-3+1000)</f>
+        <f t="shared" si="0"/>
         <v>1027</v>
       </c>
       <c r="C30" s="2" t="s">
@@ -1664,7 +1667,7 @@
     </row>
     <row r="31" spans="2:5">
       <c r="B31" s="5">
-        <f>IF(ISBLANK(C31),"",ROW()-3+1000)</f>
+        <f t="shared" si="0"/>
         <v>1028</v>
       </c>
       <c r="C31" s="2" t="s">
@@ -1679,7 +1682,7 @@
     </row>
     <row r="32" spans="2:5">
       <c r="B32" s="5">
-        <f>IF(ISBLANK(C32),"",ROW()-3+1000)</f>
+        <f t="shared" si="0"/>
         <v>1029</v>
       </c>
       <c r="C32" s="2" t="s">
@@ -1694,7 +1697,7 @@
     </row>
     <row r="33" spans="2:5">
       <c r="B33" s="5">
-        <f>IF(ISBLANK(C33),"",ROW()-3+1000)</f>
+        <f t="shared" si="0"/>
         <v>1030</v>
       </c>
       <c r="C33" s="2" t="s">
@@ -1707,15 +1710,84 @@
         <v>39</v>
       </c>
     </row>
-    <row r="34" spans="2:2">
-      <c r="B34" s="5" t="str">
-        <f>IF(ISBLANK(C34),"",ROW()-3+1000)</f>
-        <v/>
+    <row r="34" spans="2:5">
+      <c r="B34" s="5">
+        <f t="shared" si="0"/>
+        <v>1031</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="35" spans="2:2">
       <c r="B35" s="5" t="str">
-        <f>IF(ISBLANK(C35),"",ROW()-3+1000)</f>
+        <f t="shared" ref="B35:B45" si="1">IF(ISBLANK(C35),"",ROW()-3+1000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="2:2">
+      <c r="B37" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="2:2">
+      <c r="B38" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="2:2">
+      <c r="B39" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="2:2">
+      <c r="B40" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="2:2">
+      <c r="B41" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="2:2">
+      <c r="B42" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="2:2">
+      <c r="B43" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="2:2">
+      <c r="B44" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="2:2">
+      <c r="B45" s="5" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
